--- a/data/nzd0068/nzd0068.xlsx
+++ b/data/nzd0068/nzd0068.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G247"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7071,12 +7071,39 @@
         <v>289.81</v>
       </c>
       <c r="E247" t="n">
-        <v>311.2</v>
+        <v>313.37</v>
       </c>
       <c r="F247" t="n">
         <v>313.91</v>
       </c>
       <c r="G247" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>300.52</v>
+      </c>
+      <c r="C248" t="n">
+        <v>307.88</v>
+      </c>
+      <c r="D248" t="n">
+        <v>294.23</v>
+      </c>
+      <c r="E248" t="n">
+        <v>313.84</v>
+      </c>
+      <c r="F248" t="n">
+        <v>318.57</v>
+      </c>
+      <c r="G248" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7093,7 +7120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9966,6 +9993,16 @@
       </c>
       <c r="B287" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -10134,28 +10171,28 @@
         <v>0.0327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1727545967098821</v>
+        <v>0.174124209518576</v>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007737237116050122</v>
+        <v>0.007938679180661157</v>
       </c>
       <c r="M2" t="n">
-        <v>12.02311921512642</v>
+        <v>11.98012911394433</v>
       </c>
       <c r="N2" t="n">
-        <v>226.3844120540633</v>
+        <v>225.463719876187</v>
       </c>
       <c r="O2" t="n">
-        <v>15.0460763009518</v>
+        <v>15.01544937310193</v>
       </c>
       <c r="P2" t="n">
-        <v>294.2849834036842</v>
+        <v>294.271845237265</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10212,28 +10249,28 @@
         <v>0.0355</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4986932899672207</v>
+        <v>0.505384648575816</v>
       </c>
       <c r="J3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05470945999343124</v>
+        <v>0.05658242052049178</v>
       </c>
       <c r="M3" t="n">
-        <v>13.45724417142889</v>
+        <v>13.43211701270776</v>
       </c>
       <c r="N3" t="n">
-        <v>257.4204455981323</v>
+        <v>256.6459023086475</v>
       </c>
       <c r="O3" t="n">
-        <v>16.04432752090695</v>
+        <v>16.02017173155917</v>
       </c>
       <c r="P3" t="n">
-        <v>286.4315685397373</v>
+        <v>286.3681923807362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10290,28 +10327,28 @@
         <v>0.0286</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1056896529115744</v>
+        <v>-0.1080669373793474</v>
       </c>
       <c r="J4" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K4" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005035938490914993</v>
+        <v>0.005315834735574954</v>
       </c>
       <c r="M4" t="n">
-        <v>9.320424305217935</v>
+        <v>9.29510095009868</v>
       </c>
       <c r="N4" t="n">
-        <v>129.2363410574312</v>
+        <v>128.7371799295994</v>
       </c>
       <c r="O4" t="n">
-        <v>11.36821626542314</v>
+        <v>11.34624078404823</v>
       </c>
       <c r="P4" t="n">
-        <v>299.8757872885927</v>
+        <v>299.898812672073</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10368,28 +10405,28 @@
         <v>0.0384</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3251275270204583</v>
+        <v>-0.3115618867386247</v>
       </c>
       <c r="J5" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03507482523500272</v>
+        <v>0.03242862383376754</v>
       </c>
       <c r="M5" t="n">
-        <v>10.55271166789855</v>
+        <v>10.57616315945187</v>
       </c>
       <c r="N5" t="n">
-        <v>170.8802137364869</v>
+        <v>171.2109842085356</v>
       </c>
       <c r="O5" t="n">
-        <v>13.07211588597986</v>
+        <v>13.08476152662079</v>
       </c>
       <c r="P5" t="n">
-        <v>308.3075717040838</v>
+        <v>308.1768468425532</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -10446,28 +10483,28 @@
         <v>0.036</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.309629942580727</v>
+        <v>-0.2920109757141243</v>
       </c>
       <c r="J6" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K6" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03251239306297604</v>
+        <v>0.02900407448525366</v>
       </c>
       <c r="M6" t="n">
-        <v>9.816990126687216</v>
+        <v>9.86439101714981</v>
       </c>
       <c r="N6" t="n">
-        <v>167.1284976274048</v>
+        <v>168.242512750702</v>
       </c>
       <c r="O6" t="n">
-        <v>12.92781874978934</v>
+        <v>12.97083315561117</v>
       </c>
       <c r="P6" t="n">
-        <v>305.6999228194613</v>
+        <v>305.5294726576909</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -10505,7 +10542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G247"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19577,7 +19614,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>-35.33174505590481,173.18464749256702</t>
+          <t>-35.33175691098254,173.1846284970146</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -19586,6 +19623,43 @@
         </is>
       </c>
       <c r="G247" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-35.33343639849299,173.1863728111998</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-35.33289338227592,173.18576444036057</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>-35.33223557962681,173.18533998611912</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-35.3317594786718,173.18462438276975</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-35.33120208082049,173.18403903536782</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0068/nzd0068.xlsx
+++ b/data/nzd0068/nzd0068.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7104,6 +7104,33 @@
         <v>318.57</v>
       </c>
       <c r="G248" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>311.12</v>
+      </c>
+      <c r="C249" t="n">
+        <v>319.27</v>
+      </c>
+      <c r="D249" t="n">
+        <v>314.13</v>
+      </c>
+      <c r="E249" t="n">
+        <v>330.07</v>
+      </c>
+      <c r="F249" t="n">
+        <v>322.53</v>
+      </c>
+      <c r="G249" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7120,7 +7147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10003,6 +10030,16 @@
       </c>
       <c r="B288" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -10171,28 +10208,28 @@
         <v>0.0327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.174124209518576</v>
+        <v>0.1842324061635874</v>
       </c>
       <c r="J2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007938679180661157</v>
+        <v>0.00894448257286895</v>
       </c>
       <c r="M2" t="n">
-        <v>11.98012911394433</v>
+        <v>11.97852434563369</v>
       </c>
       <c r="N2" t="n">
-        <v>225.463719876187</v>
+        <v>225.1410317869084</v>
       </c>
       <c r="O2" t="n">
-        <v>15.01544937310193</v>
+        <v>15.00470032312903</v>
       </c>
       <c r="P2" t="n">
-        <v>294.271845237265</v>
+        <v>294.1745218102917</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10249,28 +10286,28 @@
         <v>0.0355</v>
       </c>
       <c r="I3" t="n">
-        <v>0.505384648575816</v>
+        <v>0.5211483510090257</v>
       </c>
       <c r="J3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05658242052049178</v>
+        <v>0.06018623873499707</v>
       </c>
       <c r="M3" t="n">
-        <v>13.43211701270776</v>
+        <v>13.44728902825928</v>
       </c>
       <c r="N3" t="n">
-        <v>256.6459023086475</v>
+        <v>257.110972589358</v>
       </c>
       <c r="O3" t="n">
-        <v>16.02017173155917</v>
+        <v>16.0346803082992</v>
       </c>
       <c r="P3" t="n">
-        <v>286.3681923807362</v>
+        <v>286.2183304817989</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10327,28 +10364,28 @@
         <v>0.0286</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1080669373793474</v>
+        <v>-0.09382585210619625</v>
       </c>
       <c r="J4" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K4" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005315834735574954</v>
+        <v>0.004015978070843196</v>
       </c>
       <c r="M4" t="n">
-        <v>9.29510095009868</v>
+        <v>9.318134623193487</v>
       </c>
       <c r="N4" t="n">
-        <v>128.7371799295994</v>
+        <v>129.393714450677</v>
       </c>
       <c r="O4" t="n">
-        <v>11.34624078404823</v>
+        <v>11.37513579921914</v>
       </c>
       <c r="P4" t="n">
-        <v>299.898812672073</v>
+        <v>299.7603720319458</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10405,28 +10442,28 @@
         <v>0.0384</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3115618867386247</v>
+        <v>-0.2865731928911906</v>
       </c>
       <c r="J5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03242862383376754</v>
+        <v>0.0272730885822412</v>
       </c>
       <c r="M5" t="n">
-        <v>10.57616315945187</v>
+        <v>10.6552917595858</v>
       </c>
       <c r="N5" t="n">
-        <v>171.2109842085356</v>
+        <v>174.1844654071844</v>
       </c>
       <c r="O5" t="n">
-        <v>13.08476152662079</v>
+        <v>13.19789624929611</v>
       </c>
       <c r="P5" t="n">
-        <v>308.1768468425532</v>
+        <v>307.9346755359408</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -10483,28 +10520,28 @@
         <v>0.036</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2920109757141243</v>
+        <v>-0.271453186759669</v>
       </c>
       <c r="J6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02900407448525366</v>
+        <v>0.02505124853763752</v>
       </c>
       <c r="M6" t="n">
-        <v>9.86439101714981</v>
+        <v>9.926121828549823</v>
       </c>
       <c r="N6" t="n">
-        <v>168.242512750702</v>
+        <v>170.0289944736523</v>
       </c>
       <c r="O6" t="n">
-        <v>12.97083315561117</v>
+        <v>13.03951665030772</v>
       </c>
       <c r="P6" t="n">
-        <v>305.5294726576909</v>
+        <v>305.3298607301535</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -10542,7 +10579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19665,6 +19702,43 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-35.33349430893199,173.18628002071358</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>-35.33295560833925,173.1856647346943</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>-35.332344297301724,173.1851657866931</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-35.33184814581258,173.18448230985837</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-35.33122371485129,173.18400437078793</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0068/nzd0068.xlsx
+++ b/data/nzd0068/nzd0068.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7133,6 +7133,60 @@
       <c r="G249" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>307.14</v>
+      </c>
+      <c r="C250" t="n">
+        <v>316.61</v>
+      </c>
+      <c r="D250" t="n">
+        <v>310.95</v>
+      </c>
+      <c r="E250" t="n">
+        <v>324.78</v>
+      </c>
+      <c r="F250" t="n">
+        <v>319.63</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:17:06+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>308.67</v>
+      </c>
+      <c r="C251" t="n">
+        <v>319.69</v>
+      </c>
+      <c r="D251" t="n">
+        <v>312.79</v>
+      </c>
+      <c r="E251" t="n">
+        <v>324.44</v>
+      </c>
+      <c r="F251" t="n">
+        <v>317.64</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10040,6 +10094,26 @@
       </c>
       <c r="B289" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -10208,28 +10282,28 @@
         <v>0.0327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1842324061635874</v>
+        <v>0.1984822752026041</v>
       </c>
       <c r="J2" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00894448257286895</v>
+        <v>0.01054340375258578</v>
       </c>
       <c r="M2" t="n">
-        <v>11.97852434563369</v>
+        <v>11.94817893715896</v>
       </c>
       <c r="N2" t="n">
-        <v>225.1410317869084</v>
+        <v>223.9289242936348</v>
       </c>
       <c r="O2" t="n">
-        <v>15.00470032312903</v>
+        <v>14.96425488601537</v>
       </c>
       <c r="P2" t="n">
-        <v>294.1745218102917</v>
+        <v>294.0370562299723</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10286,28 +10360,28 @@
         <v>0.0355</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5211483510090257</v>
+        <v>0.5496858631254258</v>
       </c>
       <c r="J3" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K3" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06018623873499707</v>
+        <v>0.06711134915760986</v>
       </c>
       <c r="M3" t="n">
-        <v>13.44728902825928</v>
+        <v>13.46453648743377</v>
       </c>
       <c r="N3" t="n">
-        <v>257.110972589358</v>
+        <v>257.5958867972006</v>
       </c>
       <c r="O3" t="n">
-        <v>16.0346803082992</v>
+        <v>16.04979397989895</v>
       </c>
       <c r="P3" t="n">
-        <v>286.2183304817989</v>
+        <v>285.9465016489244</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10364,28 +10438,28 @@
         <v>0.0286</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09382585210619625</v>
+        <v>-0.07009147493677573</v>
       </c>
       <c r="J4" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K4" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004015978070843196</v>
+        <v>0.00226016516249683</v>
       </c>
       <c r="M4" t="n">
-        <v>9.318134623193487</v>
+        <v>9.343988438036776</v>
       </c>
       <c r="N4" t="n">
-        <v>129.393714450677</v>
+        <v>130.0373746343614</v>
       </c>
       <c r="O4" t="n">
-        <v>11.37513579921914</v>
+        <v>11.4033931193466</v>
       </c>
       <c r="P4" t="n">
-        <v>299.7603720319458</v>
+        <v>299.5292070912732</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10442,28 +10516,28 @@
         <v>0.0384</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2865731928911906</v>
+        <v>-0.2472780912889826</v>
       </c>
       <c r="J5" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K5" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0272730885822412</v>
+        <v>0.02031104937073347</v>
       </c>
       <c r="M5" t="n">
-        <v>10.6552917595858</v>
+        <v>10.75997497362295</v>
       </c>
       <c r="N5" t="n">
-        <v>174.1844654071844</v>
+        <v>177.4373231790886</v>
       </c>
       <c r="O5" t="n">
-        <v>13.19789624929611</v>
+        <v>13.3205601676164</v>
       </c>
       <c r="P5" t="n">
-        <v>307.9346755359408</v>
+        <v>307.5531576768252</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -10520,28 +10594,28 @@
         <v>0.036</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.271453186759669</v>
+        <v>-0.2381766056808952</v>
       </c>
       <c r="J6" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K6" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02505124853763752</v>
+        <v>0.01940098453979389</v>
       </c>
       <c r="M6" t="n">
-        <v>9.926121828549823</v>
+        <v>10.01327327149144</v>
       </c>
       <c r="N6" t="n">
-        <v>170.0289944736523</v>
+        <v>171.9883967101623</v>
       </c>
       <c r="O6" t="n">
-        <v>13.03951665030772</v>
+        <v>13.1144346698652</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3298607301535</v>
+        <v>305.0061730936625</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -10579,7 +10653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19739,6 +19813,80 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-35.3334725652095,173.18631486093057</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>-35.33294107618434,173.18568801978898</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>-35.332326924343405,173.18519362361764</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-35.33181924569697,173.18452861708295</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-35.33120787174891,173.18402975646694</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:17:06+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-35.33348092397838,173.18630146758304</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>-35.33295790288962,173.18566105809967</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>-35.33233697662195,173.18517751671936</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-35.331817388222,173.18453159334956</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-35.33119700009969,173.1840471762892</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
